--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.410</t>
-  </si>
-  <si>
-    <t>(0.288)</t>
-  </si>
-  <si>
-    <t>6.194</t>
-  </si>
-  <si>
-    <t>(0.762)</t>
-  </si>
-  <si>
-    <t>29.088</t>
-  </si>
-  <si>
-    <t>(6.901)</t>
-  </si>
-  <si>
-    <t>41.473</t>
-  </si>
-  <si>
-    <t>(12.784)</t>
-  </si>
-  <si>
-    <t>5.185</t>
-  </si>
-  <si>
-    <t>(3.364)</t>
-  </si>
-  <si>
-    <t>7.591</t>
-  </si>
-  <si>
-    <t>(0.868)</t>
-  </si>
-  <si>
-    <t>3.227</t>
-  </si>
-  <si>
-    <t>(1.694)</t>
-  </si>
-  <si>
-    <t>2.563</t>
-  </si>
-  <si>
-    <t>(1.691)</t>
-  </si>
-  <si>
-    <t>50.052</t>
-  </si>
-  <si>
-    <t>(13.868)</t>
-  </si>
-  <si>
-    <t>33.175</t>
-  </si>
-  <si>
-    <t>(11.625)</t>
+    <t>1.473</t>
+  </si>
+  <si>
+    <t>(0.299)</t>
+  </si>
+  <si>
+    <t>6.472</t>
+  </si>
+  <si>
+    <t>(0.784)</t>
+  </si>
+  <si>
+    <t>20.492</t>
+  </si>
+  <si>
+    <t>(3.403)</t>
+  </si>
+  <si>
+    <t>25.534</t>
+  </si>
+  <si>
+    <t>(3.891)</t>
+  </si>
+  <si>
+    <t>1.549</t>
+  </si>
+  <si>
+    <t>(0.281)</t>
+  </si>
+  <si>
+    <t>7.820</t>
+  </si>
+  <si>
+    <t>(0.898)</t>
+  </si>
+  <si>
+    <t>1.284</t>
+  </si>
+  <si>
+    <t>(0.133)</t>
+  </si>
+  <si>
+    <t>0.736</t>
+  </si>
+  <si>
+    <t>(0.205)</t>
+  </si>
+  <si>
+    <t>33.144</t>
+  </si>
+  <si>
+    <t>(4.996)</t>
+  </si>
+  <si>
+    <t>18.494</t>
+  </si>
+  <si>
+    <t>(2.950)</t>
   </si>
   <si>
     <t>21</t>
@@ -198,7 +198,7 @@
     <t>(7.949)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.685</t>
-  </si>
-  <si>
-    <t>-2.051</t>
-  </si>
-  <si>
-    <t>15.584</t>
-  </si>
-  <si>
-    <t>8.300</t>
-  </si>
-  <si>
-    <t>-3.462</t>
-  </si>
-  <si>
-    <t>-0.163</t>
-  </si>
-  <si>
-    <t>-1.084</t>
-  </si>
-  <si>
-    <t>-2.052</t>
-  </si>
-  <si>
-    <t>13.216</t>
-  </si>
-  <si>
-    <t>4.045</t>
+    <t>-0.749</t>
+  </si>
+  <si>
+    <t>-2.329</t>
+  </si>
+  <si>
+    <t>24.180***</t>
+  </si>
+  <si>
+    <t>24.239**</t>
+  </si>
+  <si>
+    <t>0.174</t>
+  </si>
+  <si>
+    <t>-0.392</t>
+  </si>
+  <si>
+    <t>0.860**</t>
+  </si>
+  <si>
+    <t>-0.226</t>
+  </si>
+  <si>
+    <t>30.123**</t>
+  </si>
+  <si>
+    <t>18.726**</t>
   </si>
 </sst>
 </file>
